--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_29.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_29.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Treatment?</t>
+          <t>PracticeTrials</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Perfectionism</t>
+          <t>ExamGrade</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.8871860228268356</v>
+        <v>-1.423656266993652</v>
       </c>
       <c r="C2">
-        <v>1.18609013089063</v>
+        <v>-0.6393779563658341</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.275719841495891</v>
+        <v>-0.2095640828833245</v>
       </c>
       <c r="C3">
-        <v>0.1860505120721999</v>
+        <v>-0.07774743285124458</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.4580981896958933</v>
+        <v>-0.7303230170699693</v>
       </c>
       <c r="C4">
-        <v>-1.029183585689424</v>
+        <v>0.2036516890148796</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.2230939386270182</v>
+        <v>-0.3949610723112194</v>
       </c>
       <c r="C5">
-        <v>-0.1026485123805345</v>
+        <v>0.04788752021383777</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.8094298044518005</v>
+        <v>-1.161468858541656</v>
       </c>
       <c r="C6">
-        <v>-0.1698380056861099</v>
+        <v>0.6786334618899212</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.07856578976909499</v>
+        <v>-0.5827253267852309</v>
       </c>
       <c r="C7">
-        <v>1.091099811500579</v>
+        <v>1.1462657435433</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.03400675995177364</v>
+        <v>0.719718515241177</v>
       </c>
       <c r="C8">
-        <v>0.9201745538354777</v>
+        <v>-0.4464724358835445</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.7502415915131393</v>
+        <v>-0.8629080473126236</v>
       </c>
       <c r="C9">
-        <v>-0.1149201297169294</v>
+        <v>-0.6009089424251497</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.002424887452549151</v>
+        <v>2.063179213355714</v>
       </c>
       <c r="C10">
-        <v>-0.4425866095355031</v>
+        <v>0.9237357878780684</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-1.44525077944101</v>
+        <v>0.5603020840746838</v>
       </c>
       <c r="C11">
-        <v>0.851357937840463</v>
+        <v>0.1511909007441327</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.3650748714589722</v>
+        <v>-0.005084332552796041</v>
       </c>
       <c r="C12">
-        <v>0.4328587242593652</v>
+        <v>-0.5384984635382294</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.7137861285556274</v>
+        <v>0.155715828799136</v>
       </c>
       <c r="C13">
-        <v>-1.313157504739145</v>
+        <v>-1.060662708332337</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.3160811084005877</v>
+        <v>1.21486122446319</v>
       </c>
       <c r="C14">
-        <v>0.7401142333392078</v>
+        <v>0.8364241849827729</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.1844715073981167</v>
+        <v>-1.264513522993561</v>
       </c>
       <c r="C15">
-        <v>-0.5491405763752689</v>
+        <v>0.2617956227707978</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.1331891495933678</v>
+        <v>0.5953555915838227</v>
       </c>
       <c r="C16">
-        <v>0.003068071013643862</v>
+        <v>-2.18814771158243</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.236344997350691</v>
+        <v>0.6390380871505043</v>
       </c>
       <c r="C17">
-        <v>-0.6324879412277858</v>
+        <v>-1.441940501822216</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.2007171070160577</v>
+        <v>-2.072677822004995</v>
       </c>
       <c r="C18">
-        <v>-2.124746746620692</v>
+        <v>1.363176668517139</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-1.418395964612798</v>
+        <v>0.2128880660425967</v>
       </c>
       <c r="C19">
-        <v>1.28925953976161</v>
+        <v>0.2763226859318549</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.4428981688530542</v>
+        <v>0.7745855826766376</v>
       </c>
       <c r="C20">
-        <v>0.2680142784635973</v>
+        <v>0.1474310443451292</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.6408515480603187</v>
+        <v>-0.3681296995694844</v>
       </c>
       <c r="C21">
-        <v>-1.012605932968134</v>
+        <v>0.7559202844529768</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.875896698266161</v>
+        <v>0.6123494650418724</v>
       </c>
       <c r="C22">
-        <v>1.504381667627082</v>
+        <v>-1.498593645790621</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-2.155531275854784</v>
+        <v>0.5803348860558172</v>
       </c>
       <c r="C23">
-        <v>2.463397484883748</v>
+        <v>-0.0714653733365895</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.4787504989912658</v>
+        <v>-0.7379154066427144</v>
       </c>
       <c r="C24">
-        <v>-0.352841127777531</v>
+        <v>0.2363827611476587</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.971893123506992</v>
+        <v>-1.063916355449122</v>
       </c>
       <c r="C25">
-        <v>-0.4629215726304809</v>
+        <v>-0.3317274755611484</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.034681259606003</v>
+        <v>1.200313035837342</v>
       </c>
       <c r="C26">
-        <v>0.565477171348988</v>
+        <v>0.1685355694715566</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.3142005023547877</v>
+        <v>-0.3844725948779807</v>
       </c>
       <c r="C27">
-        <v>-0.8050246578822456</v>
+        <v>-1.438835626508682</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-1.596405579597954</v>
+        <v>0.3621380864819262</v>
       </c>
       <c r="C28">
-        <v>-0.2720510635940208</v>
+        <v>-1.0180336172711</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-3.147215636628605</v>
+        <v>3.373742587800846</v>
       </c>
       <c r="C29">
-        <v>1.013966965573471</v>
+        <v>-1.240152275422671</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.3134607829322197</v>
+        <v>-0.112289468469532</v>
       </c>
       <c r="C30">
-        <v>0.08351817454487187</v>
+        <v>0.2312484316335949</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.8337186892598569</v>
+        <v>-1.160444680717563</v>
       </c>
       <c r="C31">
-        <v>-0.5175744503143296</v>
+        <v>-0.04081958546859266</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.2277629565687325</v>
+        <v>1.332752031221385</v>
       </c>
       <c r="C32">
-        <v>0.1688044039008608</v>
+        <v>-1.007863603563522</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.2456742095214387</v>
+        <v>-0.9294961003147368</v>
       </c>
       <c r="C33">
-        <v>-0.652972471068285</v>
+        <v>0.8092795277879121</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.3147906638408189</v>
+        <v>-0.4495613522811548</v>
       </c>
       <c r="C34">
-        <v>2.134474489919667</v>
+        <v>-0.7660695142578778</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.3048873850146199</v>
+        <v>0.3923576786032179</v>
       </c>
       <c r="C35">
-        <v>-2.045248762286571</v>
+        <v>0.06962514641290216</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.9067460361186179</v>
+        <v>-0.5202959708788909</v>
       </c>
       <c r="C36">
-        <v>0.7476948114474586</v>
+        <v>-0.7210791909964165</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-1.445144849598389</v>
+        <v>0.02473363914426378</v>
       </c>
       <c r="C37">
-        <v>0.5772676956687893</v>
+        <v>0.3705507542641103</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-1.224989368830839</v>
+        <v>-0.04516176000365609</v>
       </c>
       <c r="C38">
-        <v>0.1782313534717507</v>
+        <v>0.5655780543192016</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-1.503727539588639</v>
+        <v>0.6744230036592403</v>
       </c>
       <c r="C39">
-        <v>0.7425930647856288</v>
+        <v>-0.7176328480087195</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.359352773403009</v>
+        <v>-0.4018952329028757</v>
       </c>
       <c r="C40">
-        <v>0.412078917862102</v>
+        <v>0.346655904551776</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.8471454908917597</v>
+        <v>-0.7253655443227284</v>
       </c>
       <c r="C41">
-        <v>0.7260266764637198</v>
+        <v>-2.212891044847133</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.6366737203831756</v>
+        <v>0.08917381428189121</v>
       </c>
       <c r="C42">
-        <v>0.3886101887502131</v>
+        <v>-0.6546318236224943</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.2708222042433849</v>
+        <v>0.4857326549587271</v>
       </c>
       <c r="C43">
-        <v>0.2723657663142642</v>
+        <v>-0.3304098590916882</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.3564496723355073</v>
+        <v>-0.07390476232455251</v>
       </c>
       <c r="C44">
-        <v>0.2726357518841484</v>
+        <v>1.226741515767328</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.1447320208158472</v>
+        <v>1.436760102762536</v>
       </c>
       <c r="C45">
-        <v>0.7410619924850431</v>
+        <v>1.493575083306335</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.287505568288889</v>
+        <v>-0.5062078154613194</v>
       </c>
       <c r="C46">
-        <v>0.7867221132192599</v>
+        <v>1.806837084343147</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.2095717480485866</v>
+        <v>-0.4649252154495729</v>
       </c>
       <c r="C47">
-        <v>-2.218328522133364</v>
+        <v>-0.2387846761640633</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.7302631248894392</v>
+        <v>-0.5690304671342373</v>
       </c>
       <c r="C48">
-        <v>0.5758476696603376</v>
+        <v>-0.1085976799418031</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>1.460922771507561</v>
+        <v>-0.2980086583789355</v>
       </c>
       <c r="C49">
-        <v>-2.352656090140208</v>
+        <v>-0.9524707476612053</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.9023137245219736</v>
+        <v>-0.06559108582553133</v>
       </c>
       <c r="C50">
-        <v>1.173134037915344</v>
+        <v>-0.967066563938052</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.2465470141723963</v>
+        <v>0.07333125657914788</v>
       </c>
       <c r="C51">
-        <v>-0.7951118599935449</v>
+        <v>0.1464134889344909</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>-0.8636841250829121</v>
+      </c>
+      <c r="C52">
+        <v>1.253406373186754</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>0.2752972055225403</v>
+      </c>
+      <c r="C53">
+        <v>-0.3308141327407875</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>1.080800462186165</v>
+      </c>
+      <c r="C54">
+        <v>-1.407212562138759</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>1.007004520270726</v>
+      </c>
+      <c r="C55">
+        <v>-0.06865614760809446</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>0.05312781126454631</v>
+      </c>
+      <c r="C56">
+        <v>1.108471808716354</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>-0.6171151978446064</v>
+      </c>
+      <c r="C57">
+        <v>0.8536774600491704</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>0.7581014648153178</v>
+      </c>
+      <c r="C58">
+        <v>0.6521895954520804</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>0.8557549452836788</v>
+      </c>
+      <c r="C59">
+        <v>-0.8052935422742664</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>-0.9023634052061084</v>
+      </c>
+      <c r="C60">
+        <v>0.07055652910256943</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.5007315243255497</v>
+      </c>
+      <c r="C61">
+        <v>-1.092656197121878</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>0.5774475525321637</v>
+      </c>
+      <c r="C62">
+        <v>0.1365107530367474</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>-0.009834997171567442</v>
+      </c>
+      <c r="C63">
+        <v>0.6463121337204178</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>0.5689339106919219</v>
+      </c>
+      <c r="C64">
+        <v>-1.130387787591876</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0.6969969048489906</v>
+      </c>
+      <c r="C65">
+        <v>0.2641136459812365</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>0.3457461399233439</v>
+      </c>
+      <c r="C66">
+        <v>1.038686871673882</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>0.8679240538197053</v>
+      </c>
+      <c r="C67">
+        <v>-1.946505969562843</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>0.6467520692971389</v>
+      </c>
+      <c r="C68">
+        <v>-1.475319614941197</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>-0.5375966742603661</v>
+      </c>
+      <c r="C69">
+        <v>0.1643995261263024</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>0.9779682330754242</v>
+      </c>
+      <c r="C70">
+        <v>-0.840493695856128</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>1.793993987358178</v>
+      </c>
+      <c r="C71">
+        <v>-1.626120373819565</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>-0.9112477814625271</v>
+      </c>
+      <c r="C72">
+        <v>1.80348760354679</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>0.2085292728070369</v>
+      </c>
+      <c r="C73">
+        <v>1.022926150865712</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>-0.2519452964500024</v>
+      </c>
+      <c r="C74">
+        <v>-0.1258553480315134</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>-0.8225937132623236</v>
+      </c>
+      <c r="C75">
+        <v>-0.2123644119483755</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>-0.4545400066595303</v>
+      </c>
+      <c r="C76">
+        <v>-0.4655010929270168</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>-1.058046894155945</v>
+      </c>
+      <c r="C77">
+        <v>0.9514714183002757</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>0.4362831883527009</v>
+      </c>
+      <c r="C78">
+        <v>0.6122792999149043</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>1.730771253857344</v>
+      </c>
+      <c r="C79">
+        <v>-1.857261869339918</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>1.334751766697005</v>
+      </c>
+      <c r="C80">
+        <v>-1.962046185548969</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>-0.3358317766831839</v>
+      </c>
+      <c r="C81">
+        <v>0.5615689901647931</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>-0.4363245903828597</v>
+      </c>
+      <c r="C82">
+        <v>0.4177928615916648</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>-1.231332214494955</v>
+      </c>
+      <c r="C83">
+        <v>2.056500931890266</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>-0.3868809851335753</v>
+      </c>
+      <c r="C84">
+        <v>-0.2450788846283849</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>-1.080860730889024</v>
+      </c>
+      <c r="C85">
+        <v>0.4463313323135109</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>-0.4233350724234263</v>
+      </c>
+      <c r="C86">
+        <v>-0.1299543926412634</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>-0.5048586721278274</v>
+      </c>
+      <c r="C87">
+        <v>0.3481630972329542</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>-0.0238799901126231</v>
+      </c>
+      <c r="C88">
+        <v>-0.06447578870991971</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>0.2348725748773556</v>
+      </c>
+      <c r="C89">
+        <v>-1.282346022573233</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>0.04151592758047805</v>
+      </c>
+      <c r="C90">
+        <v>0.2462834942221263</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>-2.254934505241329</v>
+      </c>
+      <c r="C91">
+        <v>1.882959279635495</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>-0.1815886841471943</v>
+      </c>
+      <c r="C92">
+        <v>0.8568441013389884</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>0.5903759704728538</v>
+      </c>
+      <c r="C93">
+        <v>-0.7115568155275177</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>0.4034785640943963</v>
+      </c>
+      <c r="C94">
+        <v>1.700553991659928</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>0.1465715132346097</v>
+      </c>
+      <c r="C95">
+        <v>0.9486828324808594</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>0.1728864126527322</v>
+      </c>
+      <c r="C96">
+        <v>0.4230833682053937</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>0.3053014290383715</v>
+      </c>
+      <c r="C97">
+        <v>0.4304727700272801</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>-1.344502338080294</v>
+      </c>
+      <c r="C98">
+        <v>0.9810288229957869</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>1.997711574208708</v>
+      </c>
+      <c r="C99">
+        <v>-0.8188252005557388</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>-0.4988454328261424</v>
+      </c>
+      <c r="C100">
+        <v>-0.2753324789875763</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>0.882501932030339</v>
+      </c>
+      <c r="C101">
+        <v>0.6569764231441706</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-1.444550312029971</v>
+      </c>
+      <c r="C102">
+        <v>0.1791324954341083</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>0.8916689569958373</v>
+      </c>
+      <c r="C103">
+        <v>-1.445822109153076</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-0.8159377356783838</v>
+      </c>
+      <c r="C104">
+        <v>-0.9474805363733061</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>0.8670046066748928</v>
+      </c>
+      <c r="C105">
+        <v>0.685367863219146</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>2.295710964713579</v>
+      </c>
+      <c r="C106">
+        <v>-2.451131071492182</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>-1.49489780876017</v>
+      </c>
+      <c r="C107">
+        <v>2.155359786820158</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>1.285100514716821</v>
+      </c>
+      <c r="C108">
+        <v>0.2278272661785143</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>-1.650884832817267</v>
+      </c>
+      <c r="C109">
+        <v>-0.06075507084471232</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-0.8262596330510432</v>
+      </c>
+      <c r="C110">
+        <v>-0.1677521151747177</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>2.086729592482746</v>
+      </c>
+      <c r="C111">
+        <v>-0.8887764576486777</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>-0.04272591154854917</v>
+      </c>
+      <c r="C112">
+        <v>-0.2028197464219724</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>0.3315628852006386</v>
+      </c>
+      <c r="C113">
+        <v>-1.252037905640583</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-1.48077505089169</v>
+      </c>
+      <c r="C114">
+        <v>1.933955512141291</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-0.9963096334732888</v>
+      </c>
+      <c r="C115">
+        <v>1.130199561127131</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>0.2237396365508532</v>
+      </c>
+      <c r="C116">
+        <v>-0.1463659278194475</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-0.1620163845667644</v>
+      </c>
+      <c r="C117">
+        <v>-0.2918677510178082</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.7242330073921162</v>
+      </c>
+      <c r="C118">
+        <v>0.8097302785022129</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>1.425167546751653</v>
+      </c>
+      <c r="C119">
+        <v>-1.094306285537639</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-1.448758023122426</v>
+      </c>
+      <c r="C120">
+        <v>-0.03136117099945301</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>0.3249911086428528</v>
+      </c>
+      <c r="C121">
+        <v>-1.356246257496203</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-2.471637535693203</v>
+      </c>
+      <c r="C122">
+        <v>0.9017197148629398</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.612056796809536</v>
+      </c>
+      <c r="C123">
+        <v>0.3733711025928043</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>-0.6360633779034952</v>
+      </c>
+      <c r="C124">
+        <v>1.351441386908677</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>-0.06189451184680392</v>
+      </c>
+      <c r="C125">
+        <v>-0.4244019531041955</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-0.8533525957276779</v>
+      </c>
+      <c r="C126">
+        <v>1.71784448785983</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-0.2522646362842828</v>
+      </c>
+      <c r="C127">
+        <v>0.04722032525008867</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>0.06100794540725561</v>
+      </c>
+      <c r="C128">
+        <v>1.046276723511449</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>-0.7686052886941102</v>
+      </c>
+      <c r="C129">
+        <v>0.6061673305902335</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.3723078672986133</v>
+      </c>
+      <c r="C130">
+        <v>-1.380912582663401</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>1.184873041604662</v>
+      </c>
+      <c r="C131">
+        <v>-1.079134991087256</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-0.6188388272064567</v>
+      </c>
+      <c r="C132">
+        <v>-0.6282673086800277</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.07124261108610978</v>
+      </c>
+      <c r="C133">
+        <v>1.059506625466343</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>-6.32900167846273E-05</v>
+      </c>
+      <c r="C134">
+        <v>-0.3344976476132533</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.06445622427189925</v>
+      </c>
+      <c r="C135">
+        <v>0.5558252433323</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>0.1605295191738605</v>
+      </c>
+      <c r="C136">
+        <v>-0.3742269643264615</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-1.082735636133157</v>
+      </c>
+      <c r="C137">
+        <v>-0.09983666935243091</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>-0.9358208389517468</v>
+      </c>
+      <c r="C138">
+        <v>-0.4797423666262655</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>-0.4304473790956467</v>
+      </c>
+      <c r="C139">
+        <v>0.4633010195798495</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.1862506684539356</v>
+      </c>
+      <c r="C140">
+        <v>-0.9959734969139193</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>-0.2802990074266369</v>
+      </c>
+      <c r="C141">
+        <v>-0.04944495669416633</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>2.155259644031006</v>
+      </c>
+      <c r="C142">
+        <v>0.78115024765495</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-0.5018626612767374</v>
+      </c>
+      <c r="C143">
+        <v>-0.4433302408858306</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.8764125577639206</v>
+      </c>
+      <c r="C144">
+        <v>0.405623492124105</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>-1.93666839043916</v>
+      </c>
+      <c r="C145">
+        <v>1.26382744306483</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>1.339971022397107</v>
+      </c>
+      <c r="C146">
+        <v>-0.8395010438506332</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-1.072101899232265</v>
+      </c>
+      <c r="C147">
+        <v>0.03077310335010586</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.5483716663548679</v>
+      </c>
+      <c r="C148">
+        <v>-0.6582186080913661</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-0.2039135545464342</v>
+      </c>
+      <c r="C149">
+        <v>-0.6751067526457766</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>-0.140383309543252</v>
+      </c>
+      <c r="C150">
+        <v>0.3166708333281048</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>-0.6775450588866466</v>
+      </c>
+      <c r="C151">
+        <v>2.19781917786942</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>0.4617106213417935</v>
+      </c>
+      <c r="C152">
+        <v>0.245871728099115</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>1.040089308101009</v>
+      </c>
+      <c r="C153">
+        <v>0.5186434778033542</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-0.02662060704552616</v>
+      </c>
+      <c r="C154">
+        <v>-1.139519952419632</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>1.218533414391889</v>
+      </c>
+      <c r="C155">
+        <v>-0.2378287760148644</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>1.129778194802942</v>
+      </c>
+      <c r="C156">
+        <v>0.8618310931676645</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.9446089293467355</v>
+      </c>
+      <c r="C157">
+        <v>1.551541353523733</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>0.1829072561103856</v>
+      </c>
+      <c r="C158">
+        <v>0.653636313447713</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-1.983012359651882</v>
+      </c>
+      <c r="C159">
+        <v>1.883801509742344</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>-0.6118977508088737</v>
+      </c>
+      <c r="C160">
+        <v>-0.03699274750233816</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-0.2927679367110927</v>
+      </c>
+      <c r="C161">
+        <v>1.015517444534942</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-1.825301649459431</v>
+      </c>
+      <c r="C162">
+        <v>0.6187524713190694</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.1466620217927528</v>
+      </c>
+      <c r="C163">
+        <v>-1.820463660773654</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>1.268231163979981</v>
+      </c>
+      <c r="C164">
+        <v>-0.8832708326997267</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>0.4931854686030735</v>
+      </c>
+      <c r="C165">
+        <v>0.4204205237963679</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>1.261654738251355</v>
+      </c>
+      <c r="C166">
+        <v>-2.638137381755554</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-0.814513012424056</v>
+      </c>
+      <c r="C167">
+        <v>-1.209495957290471</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>1.535331410631674</v>
+      </c>
+      <c r="C168">
+        <v>1.124465422875755</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>1.057224453759181</v>
+      </c>
+      <c r="C169">
+        <v>-0.8594676506730667</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>0.09036191025623089</v>
+      </c>
+      <c r="C170">
+        <v>0.9547949858887417</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>-1.183883010427021</v>
+      </c>
+      <c r="C171">
+        <v>0.8484352874581795</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>-0.3763987862921957</v>
+      </c>
+      <c r="C172">
+        <v>1.499466818078677</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>1.295190095731968</v>
+      </c>
+      <c r="C173">
+        <v>-0.5478992963541852</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>1.276335740250665</v>
+      </c>
+      <c r="C174">
+        <v>-0.0367872778171392</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>0.7591006711096099</v>
+      </c>
+      <c r="C175">
+        <v>-1.957544523272081</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>1.224297402300605</v>
+      </c>
+      <c r="C176">
+        <v>-0.7864129289312308</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-0.1488232144157192</v>
+      </c>
+      <c r="C177">
+        <v>0.2228244697464933</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>-0.5731882010440771</v>
+      </c>
+      <c r="C178">
+        <v>0.4243048678709775</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.789442324801982</v>
+      </c>
+      <c r="C179">
+        <v>1.00955967382252</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>0.3159629461177458</v>
+      </c>
+      <c r="C180">
+        <v>-0.2087648760491378</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>0.1235849154500428</v>
+      </c>
+      <c r="C181">
+        <v>-1.469870209251588</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0.7007819379436171</v>
+      </c>
+      <c r="C182">
+        <v>1.781004450848807</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>1.311858562726396</v>
+      </c>
+      <c r="C183">
+        <v>-0.3985896170477767</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.2845735637521858</v>
+      </c>
+      <c r="C184">
+        <v>-0.4311546567107874</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>0.6207050685913442</v>
+      </c>
+      <c r="C185">
+        <v>-0.3925758905529698</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>0.01377047778868397</v>
+      </c>
+      <c r="C186">
+        <v>0.8058480066698611</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-1.443932260756854</v>
+      </c>
+      <c r="C187">
+        <v>-0.540003860637987</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-2.187466518698658</v>
+      </c>
+      <c r="C188">
+        <v>-0.06084980046299182</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.5006620656213419</v>
+      </c>
+      <c r="C189">
+        <v>0.3655708952951552</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>-1.014971268850502</v>
+      </c>
+      <c r="C190">
+        <v>-0.6697403759793625</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-1.316930720309022</v>
+      </c>
+      <c r="C191">
+        <v>0.6663448375434723</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.8063510091717984</v>
+      </c>
+      <c r="C192">
+        <v>0.6670633736241183</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-1.602353310990498</v>
+      </c>
+      <c r="C193">
+        <v>1.052576838982906</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>0.4968182427113082</v>
+      </c>
+      <c r="C194">
+        <v>0.5130016719457744</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>1.375723960223347</v>
+      </c>
+      <c r="C195">
+        <v>-0.006722298293428852</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>-0.9814525618128168</v>
+      </c>
+      <c r="C196">
+        <v>0.853357589212896</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>3.478458717929784</v>
+      </c>
+      <c r="C197">
+        <v>-1.517583456987974</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>0.03936394507231823</v>
+      </c>
+      <c r="C198">
+        <v>0.1308376880243361</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.804922357237524</v>
+      </c>
+      <c r="C199">
+        <v>-1.179510165348368</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-0.2383280872877722</v>
+      </c>
+      <c r="C200">
+        <v>0.1756798475408389</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-0.1146234487263009</v>
+      </c>
+      <c r="C201">
+        <v>-0.7889000442547585</v>
       </c>
     </row>
   </sheetData>
